--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9816,0.0080,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9504,0.0121,0.0157,0.0030</t>
-  </si>
-  <si>
-    <t>0.9137,0.0699,0.0124,0.0011</t>
-  </si>
-  <si>
-    <t>0.8776,0.0775,0.0070,0.0061</t>
-  </si>
-  <si>
-    <t>0.9693,0.0413,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9611,0.0332,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.8807,0.1624,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.9241,0.0833,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.9128,0.0945,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.8609,0.2103,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.8376,0.2261,0.0062,0.0013</t>
-  </si>
-  <si>
-    <t>0.6751,0.4249,0.0031,0.0013</t>
-  </si>
-  <si>
-    <t>0.9791,0.0104,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.9153,0.0390,0.0232,0.0004</t>
-  </si>
-  <si>
-    <t>0.9716,0.0049,0.0223,0.0006</t>
-  </si>
-  <si>
-    <t>0.9872,0.0020,0.0103,0.0002</t>
-  </si>
-  <si>
-    <t>0.9029,0.0654,0.0265,0.0009</t>
-  </si>
-  <si>
-    <t>0.7011,0.4951,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.7258,0.3737,0.0099,0.0002</t>
-  </si>
-  <si>
-    <t>0.9046,0.1660,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.2598,0.8812,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.2848,0.8522,0.0042,0.0004</t>
-  </si>
-  <si>
-    <t>0.9520,0.0080,0.0496,0.0007</t>
-  </si>
-  <si>
-    <t>0.9892,0.0026,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.1902,0.0080,0.8767,0.0010</t>
-  </si>
-  <si>
-    <t>0.9517,0.0121,0.0251,0.0002</t>
-  </si>
-  <si>
-    <t>0.8112,0.0328,0.1868,0.0013</t>
-  </si>
-  <si>
-    <t>0.9514,0.0032,0.0636,0.0002</t>
-  </si>
-  <si>
-    <t>0.6217,0.0040,0.5884,0.0002</t>
-  </si>
-  <si>
-    <t>0.9205,0.1368,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9256,0.0601,0.0088,0.0008</t>
-  </si>
-  <si>
-    <t>0.0269,0.4235,0.8727,0.0010</t>
-  </si>
-  <si>
-    <t>0.9834,0.0141,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.9373,0.0756,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.7741,0.2681,0.0153,0.0014</t>
-  </si>
-  <si>
-    <t>0.8089,0.2501,0.0078,0.0012</t>
-  </si>
-  <si>
-    <t>0.9768,0.0176,0.0056,0.0002</t>
-  </si>
-  <si>
-    <t>0.3657,0.1768,0.2392,0.0018</t>
-  </si>
-  <si>
-    <t>0.9761,0.0007,0.0439,0.0003</t>
-  </si>
-  <si>
-    <t>0.9868,0.0005,0.0301,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0006,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.6944,0.0063,0.3185,0.0001</t>
-  </si>
-  <si>
-    <t>0.2070,0.1609,0.2260,0.0004</t>
-  </si>
-  <si>
-    <t>0.9616,0.0015,0.0875,0.0001</t>
-  </si>
-  <si>
-    <t>0.9015,0.0985,0.0122,0.0006</t>
-  </si>
-  <si>
-    <t>0.9154,0.1140,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.9565,0.0403,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.7527,0.2135,0.0314,0.0007</t>
-  </si>
-  <si>
-    <t>0.0223,0.0015,0.9838,0.0004</t>
-  </si>
-  <si>
-    <t>0.1948,0.0112,0.8926,0.0007</t>
-  </si>
-  <si>
-    <t>0.9803,0.0027,0.0187,0.0001</t>
-  </si>
-  <si>
-    <t>0.8696,0.0064,0.2499,0.0010</t>
-  </si>
-  <si>
-    <t>0.0856,0.0076,0.9379,0.0001</t>
-  </si>
-  <si>
-    <t>0.8864,0.0027,0.2281,0.0005</t>
-  </si>
-  <si>
-    <t>0.7917,0.2843,0.0069,0.0011</t>
-  </si>
-  <si>
-    <t>0.9321,0.0485,0.0042,0.0018</t>
-  </si>
-  <si>
-    <t>0.7770,0.3152,0.0104,0.0007</t>
-  </si>
-  <si>
-    <t>0.4829,0.4698,0.0848,0.0041</t>
-  </si>
-  <si>
-    <t>0.9597,0.0432,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9444,0.0612,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.7896,0.3827,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.4357,0.4607,0.0534,0.0002</t>
-  </si>
-  <si>
-    <t>0.5019,0.0028,0.7292,0.0008</t>
-  </si>
-  <si>
-    <t>0.0698,0.1173,0.7932,0.0048</t>
-  </si>
-  <si>
-    <t>0.4336,0.2994,0.0480,0.0000</t>
-  </si>
-  <si>
-    <t>0.2254,0.1547,0.6468,0.0044</t>
-  </si>
-  <si>
-    <t>0.7114,0.3595,0.0108,0.0002</t>
-  </si>
-  <si>
-    <t>0.0200,0.9890,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9563,0.0303,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.9720,0.0229,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.0878,0.7853,0.1486,0.0012</t>
-  </si>
-  <si>
-    <t>0.7439,0.0243,0.2583,0.0002</t>
-  </si>
-  <si>
-    <t>0.9433,0.0109,0.0526,0.0004</t>
-  </si>
-  <si>
-    <t>0.2510,0.5985,0.0901,0.0003</t>
-  </si>
-  <si>
-    <t>0.0808,0.6423,0.5292,0.0003</t>
-  </si>
-  <si>
-    <t>0.9485,0.0091,0.0305,0.0060</t>
-  </si>
-  <si>
-    <t>0.9755,0.0111,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9346,0.0129,0.0139,0.0085</t>
-  </si>
-  <si>
-    <t>0.9709,0.0105,0.0014,0.0029</t>
-  </si>
-  <si>
-    <t>0.9780,0.0100,0.0035,0.0018</t>
-  </si>
-  <si>
-    <t>0.9672,0.0156,0.0046,0.0017</t>
-  </si>
-  <si>
-    <t>0.7168,0.1424,0.0412,0.0001</t>
-  </si>
-  <si>
-    <t>0.4451,0.0634,0.3504,0.0003</t>
-  </si>
-  <si>
-    <t>0.8790,0.0095,0.1497,0.0008</t>
-  </si>
-  <si>
-    <t>0.9840,0.0009,0.0346,0.0002</t>
-  </si>
-  <si>
-    <t>0.8553,0.0352,0.0594,0.0001</t>
-  </si>
-  <si>
-    <t>0.7830,0.0550,0.0718,0.0002</t>
-  </si>
-  <si>
-    <t>0.9450,0.0624,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.8915,0.1563,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9593,0.0373,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.9550,0.0536,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9185,0.1014,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.9081,0.1001,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.7304,0.3271,0.0220,0.0022</t>
-  </si>
-  <si>
-    <t>0.7965,0.2711,0.0063,0.0015</t>
-  </si>
-  <si>
-    <t>0.9141,0.0913,0.0028,0.0012</t>
-  </si>
-  <si>
-    <t>0.5828,0.4903,0.0079,0.0017</t>
-  </si>
-  <si>
-    <t>0.9269,0.0878,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9593,0.0396,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.8545,0.2095,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.8984,0.1312,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.8979,0.1289,0.0035,0.0012</t>
-  </si>
-  <si>
-    <t>0.8829,0.1668,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.0509,0.0232,0.9587,0.0010</t>
-  </si>
-  <si>
-    <t>0.9925,0.0011,0.0056,0.0001</t>
-  </si>
-  <si>
-    <t>0.9901,0.0014,0.0070,0.0002</t>
-  </si>
-  <si>
-    <t>0.9880,0.0022,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.3050,0.7633,0.0174,0.0004</t>
-  </si>
-  <si>
-    <t>0.0493,0.9604,0.0121,0.0002</t>
-  </si>
-  <si>
-    <t>0.5731,0.5921,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.9511,0.0819,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0206,0.9825,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.0151,0.9833,0.0049,0.0002</t>
-  </si>
-  <si>
-    <t>0.9761,0.0251,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9646,0.0184,0.0064,0.0007</t>
-  </si>
-  <si>
-    <t>0.9861,0.0035,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.9713,0.0137,0.0075,0.0002</t>
-  </si>
-  <si>
-    <t>0.9782,0.0124,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.9151,0.0284,0.0386,0.0028</t>
-  </si>
-  <si>
-    <t>0.7264,0.4313,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9147,0.1366,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.8312,0.2019,0.0081,0.0003</t>
-  </si>
-  <si>
-    <t>0.6050,0.0790,0.1192,0.0003</t>
-  </si>
-  <si>
-    <t>0.9717,0.0327,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.8253,0.2740,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.8376,0.2052,0.0056,0.0008</t>
-  </si>
-  <si>
-    <t>0.9572,0.0438,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.8782,0.1561,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.8196,0.1702,0.0054,0.0027</t>
-  </si>
-  <si>
-    <t>0.9403,0.0503,0.0067,0.0013</t>
-  </si>
-  <si>
-    <t>0.9298,0.0607,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.8888,0.1382,0.0074,0.0009</t>
-  </si>
-  <si>
-    <t>0.9241,0.0913,0.0043,0.0007</t>
-  </si>
-  <si>
-    <t>0.9025,0.0855,0.0041,0.0022</t>
-  </si>
-  <si>
-    <t>0.7900,0.0021,0.4861,0.0002</t>
-  </si>
-  <si>
-    <t>0.2115,0.0305,0.8154,0.0003</t>
-  </si>
-  <si>
-    <t>0.9704,0.0016,0.0546,0.0002</t>
-  </si>
-  <si>
-    <t>0.9638,0.0033,0.0474,0.0001</t>
-  </si>
-  <si>
-    <t>0.9908,0.0062,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9731,0.0201,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9548,0.0145,0.0256,0.0009</t>
-  </si>
-  <si>
-    <t>0.9675,0.0175,0.0065,0.0005</t>
-  </si>
-  <si>
-    <t>0.9647,0.0192,0.0030,0.0018</t>
-  </si>
-  <si>
-    <t>0.9410,0.0071,0.0180,0.0125</t>
-  </si>
-  <si>
-    <t>0.9198,0.0395,0.0184,0.0051</t>
-  </si>
-  <si>
-    <t>0.9491,0.0165,0.0069,0.0036</t>
-  </si>
-  <si>
-    <t>0.3257,0.0545,0.6133,0.0007</t>
-  </si>
-  <si>
-    <t>0.8497,0.1927,0.0074,0.0029</t>
-  </si>
-  <si>
-    <t>0.9098,0.0909,0.0023,0.0012</t>
-  </si>
-  <si>
-    <t>0.9347,0.0679,0.0027,0.0011</t>
-  </si>
-  <si>
-    <t>0.9386,0.0636,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.8237,0.2002,0.0038,0.0013</t>
-  </si>
-  <si>
-    <t>0.8547,0.1541,0.0069,0.0015</t>
-  </si>
-  <si>
-    <t>0.9323,0.0996,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.6451,0.1598,0.2779,0.0116</t>
-  </si>
-  <si>
-    <t>0.9246,0.0640,0.0049,0.0013</t>
-  </si>
-  <si>
-    <t>0.8561,0.1274,0.0187,0.0037</t>
-  </si>
-  <si>
-    <t>0.9441,0.0695,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9859,0.0052,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9301,0.0741,0.0073,0.0002</t>
-  </si>
-  <si>
-    <t>0.9269,0.0990,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9371,0.0787,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.9498,0.0548,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9525,0.0480,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.8653,0.1476,0.0065,0.0017</t>
-  </si>
-  <si>
-    <t>0.9274,0.0899,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9018,0.1050,0.0038,0.0011</t>
-  </si>
-  <si>
-    <t>0.9377,0.0537,0.0049,0.0016</t>
-  </si>
-  <si>
-    <t>0.9353,0.0726,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.9032,0.1041,0.0036,0.0015</t>
-  </si>
-  <si>
-    <t>0.8709,0.1363,0.0112,0.0022</t>
-  </si>
-  <si>
-    <t>0.9470,0.0598,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9060,0.1231,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.7420,0.3734,0.0090,0.0005</t>
-  </si>
-  <si>
-    <t>0.9511,0.0279,0.0068,0.0014</t>
-  </si>
-  <si>
-    <t>0.9191,0.1019,0.0051,0.0007</t>
-  </si>
-  <si>
-    <t>0.8549,0.1726,0.0071,0.0013</t>
-  </si>
-  <si>
-    <t>0.8843,0.1344,0.0060,0.0013</t>
-  </si>
-  <si>
-    <t>0.8729,0.2060,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0216,0.3155,0.9419,0.0020</t>
-  </si>
-  <si>
-    <t>0.8743,0.1928,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.6803,0.0076,0.4698,0.0011</t>
-  </si>
-  <si>
-    <t>0.8513,0.0014,0.3747,0.0002</t>
-  </si>
-  <si>
-    <t>0.7316,0.0286,0.3672,0.0077</t>
-  </si>
-  <si>
-    <t>0.3983,0.0028,0.8685,0.0001</t>
-  </si>
-  <si>
-    <t>0.9603,0.0019,0.0624,0.0008</t>
-  </si>
-  <si>
-    <t>0.8802,0.0022,0.2489,0.0003</t>
-  </si>
-  <si>
-    <t>0.0935,0.0847,0.9015,0.0017</t>
-  </si>
-  <si>
-    <t>0.7221,0.3375,0.0182,0.0007</t>
-  </si>
-  <si>
-    <t>0.9856,0.0050,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.9390,0.0388,0.0183,0.0008</t>
-  </si>
-  <si>
-    <t>0.9298,0.0602,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.9438,0.0172,0.0234,0.0002</t>
-  </si>
-  <si>
-    <t>0.9693,0.0105,0.0102,0.0004</t>
-  </si>
-  <si>
-    <t>0.9436,0.0317,0.0133,0.0007</t>
-  </si>
-  <si>
-    <t>0.9767,0.0050,0.0104,0.0007</t>
-  </si>
-  <si>
-    <t>0.5404,0.6639,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.8126,0.3137,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9587,0.0507,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.8936,0.1373,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.9010,0.1548,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.9718,0.0111,0.0118,0.0003</t>
-  </si>
-  <si>
-    <t>0.9747,0.0058,0.0102,0.0010</t>
-  </si>
-  <si>
-    <t>0.9841,0.0043,0.0057,0.0002</t>
-  </si>
-  <si>
-    <t>0.9730,0.0101,0.0122,0.0002</t>
-  </si>
-  <si>
-    <t>0.9142,0.0170,0.0589,0.0009</t>
-  </si>
-  <si>
-    <t>0.5472,0.0891,0.3543,0.0029</t>
-  </si>
-  <si>
-    <t>0.6098,0.0129,0.5572,0.0023</t>
-  </si>
-  <si>
-    <t>0.9949,0.0002,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.9925,0.0009,0.0062,0.0001</t>
-  </si>
-  <si>
-    <t>0.9904,0.0007,0.0168,0.0001</t>
-  </si>
-  <si>
-    <t>0.8084,0.2197,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.9434,0.0419,0.0020,0.0015</t>
-  </si>
-  <si>
-    <t>0.9647,0.0316,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.9663,0.0403,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.8360,0.2310,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.9179,0.0791,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.9693,0.0196,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9276,0.0641,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.7067,0.0753,0.2014,0.0020</t>
-  </si>
-  <si>
-    <t>0.9459,0.0262,0.0130,0.0008</t>
-  </si>
-  <si>
-    <t>0.8809,0.1871,0.0048,0.0004</t>
-  </si>
-  <si>
-    <t>0.1680,0.0215,0.9145,0.0008</t>
-  </si>
-  <si>
-    <t>0.0852,0.0683,0.9050,0.0026</t>
-  </si>
-  <si>
-    <t>0.7223,0.0181,0.3279,0.0050</t>
-  </si>
-  <si>
-    <t>0.0218,0.0018,0.9908,0.0001</t>
-  </si>
-  <si>
-    <t>0.9489,0.0092,0.0615,0.0008</t>
-  </si>
-  <si>
-    <t>0.0389,0.0781,0.9123,0.0037</t>
-  </si>
-  <si>
-    <t>0.9423,0.0033,0.0926,0.0004</t>
-  </si>
-  <si>
-    <t>0.9570,0.0202,0.0143,0.0007</t>
-  </si>
-  <si>
-    <t>0.9884,0.0021,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.9910,0.0011,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.9827,0.0048,0.0070,0.0003</t>
-  </si>
-  <si>
-    <t>0.8971,0.1425,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9787,0.0162,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.8660,0.2030,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.7229,0.3484,0.0078,0.0019</t>
-  </si>
-  <si>
-    <t>0.8096,0.2221,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.9153,0.0883,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.9739,0.0223,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.7975,0.2480,0.0050,0.0024</t>
-  </si>
-  <si>
-    <t>0.6541,0.0620,0.1676,0.0007</t>
-  </si>
-  <si>
-    <t>0.5130,0.0153,0.5839,0.0002</t>
-  </si>
-  <si>
-    <t>0.9257,0.0092,0.0961,0.0005</t>
-  </si>
-  <si>
-    <t>0.9167,0.0214,0.0591,0.0010</t>
-  </si>
-  <si>
-    <t>0.0225,0.0071,0.9779,0.0015</t>
-  </si>
-  <si>
-    <t>0.8401,0.0138,0.1975,0.0014</t>
-  </si>
-  <si>
-    <t>0.9394,0.0104,0.0622,0.0011</t>
-  </si>
-  <si>
-    <t>0.9654,0.0016,0.0559,0.0004</t>
-  </si>
-  <si>
-    <t>0.9632,0.0306,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.9237,0.0376,0.0235,0.0038</t>
-  </si>
-  <si>
-    <t>0.9451,0.0226,0.0024,0.0049</t>
-  </si>
-  <si>
-    <t>0.9645,0.0053,0.0054,0.0085</t>
-  </si>
-  <si>
-    <t>0.9818,0.0028,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.8933,0.0796,0.0227,0.0013</t>
+    <t>0.8164,0.0216,0.0502,0.1067</t>
+  </si>
+  <si>
+    <t>0.0256,0.0071,0.0003,0.9878</t>
+  </si>
+  <si>
+    <t>0.9224,0.0011,0.0004,0.0804</t>
+  </si>
+  <si>
+    <t>0.0127,0.0070,0.0017,0.9926</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9938,0.0048,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0012,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9699,0.0103,0.0093,0.0004</t>
+  </si>
+  <si>
+    <t>0.0384,0.0040,0.9676,0.0004</t>
+  </si>
+  <si>
+    <t>0.7929,0.0013,0.4183,0.0001</t>
+  </si>
+  <si>
+    <t>0.0918,0.0159,0.9106,0.0048</t>
+  </si>
+  <si>
+    <t>0.9605,0.0016,0.0658,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.9979,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.0292,0.9673,0.0036,0.0083</t>
+  </si>
+  <si>
+    <t>0.0152,0.9822,0.0019,0.0018</t>
+  </si>
+  <si>
+    <t>0.0442,0.9658,0.0020,0.0016</t>
+  </si>
+  <si>
+    <t>0.0043,0.9907,0.0039,0.0046</t>
+  </si>
+  <si>
+    <t>0.5977,0.0153,0.5189,0.0077</t>
+  </si>
+  <si>
+    <t>0.4947,0.0014,0.6494,0.0020</t>
+  </si>
+  <si>
+    <t>0.0201,0.0009,0.9816,0.0010</t>
+  </si>
+  <si>
+    <t>0.0584,0.0021,0.9402,0.0049</t>
+  </si>
+  <si>
+    <t>0.0922,0.0022,0.9589,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.0021,0.9898,0.0011</t>
+  </si>
+  <si>
+    <t>0.0036,0.0004,0.9930,0.0014</t>
+  </si>
+  <si>
+    <t>0.2090,0.7901,0.0081,0.0625</t>
+  </si>
+  <si>
+    <t>0.6790,0.2108,0.1705,0.0224</t>
+  </si>
+  <si>
+    <t>0.0190,0.0069,0.9808,0.0011</t>
+  </si>
+  <si>
+    <t>0.0054,0.6039,0.5818,0.0001</t>
+  </si>
+  <si>
+    <t>0.8541,0.0505,0.0764,0.0205</t>
+  </si>
+  <si>
+    <t>0.4071,0.1321,0.5150,0.0041</t>
+  </si>
+  <si>
+    <t>0.8030,0.3960,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.0115,0.9798,0.0394,0.0006</t>
+  </si>
+  <si>
+    <t>0.0055,0.0562,0.9752,0.0099</t>
+  </si>
+  <si>
+    <t>0.4370,0.0126,0.6731,0.0111</t>
+  </si>
+  <si>
+    <t>0.0465,0.0052,0.9682,0.0015</t>
+  </si>
+  <si>
+    <t>0.1545,0.0017,0.8895,0.0034</t>
+  </si>
+  <si>
+    <t>0.0121,0.2620,0.9771,0.0037</t>
+  </si>
+  <si>
+    <t>0.0064,0.9489,0.0247,0.0012</t>
+  </si>
+  <si>
+    <t>0.0128,0.0032,0.9828,0.0020</t>
+  </si>
+  <si>
+    <t>0.5848,0.0785,0.0073,0.2832</t>
+  </si>
+  <si>
+    <t>0.0007,0.9971,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.0047,0.9712,0.0328,0.0033</t>
+  </si>
+  <si>
+    <t>0.0023,0.9895,0.0119,0.0027</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9980,0.0010</t>
+  </si>
+  <si>
+    <t>0.0014,0.0098,0.9970,0.0005</t>
+  </si>
+  <si>
+    <t>0.0169,0.0023,0.9815,0.0018</t>
+  </si>
+  <si>
+    <t>0.0109,0.0012,0.9943,0.0002</t>
+  </si>
+  <si>
+    <t>0.0132,0.0043,0.9847,0.0024</t>
+  </si>
+  <si>
+    <t>0.0015,0.0035,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.8629,0.2402,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9799,0.0029,0.0134,0.0018</t>
+  </si>
+  <si>
+    <t>0.9878,0.0057,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.0182,0.0083,0.9847,0.0023</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0011,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9947,0.0034,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9642,0.9641,0.0009</t>
+  </si>
+  <si>
+    <t>0.0128,0.0007,0.9905,0.0005</t>
+  </si>
+  <si>
+    <t>0.0142,0.0058,0.9832,0.0025</t>
+  </si>
+  <si>
+    <t>0.0002,0.9937,0.9608,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9987,0.0004</t>
+  </si>
+  <si>
+    <t>0.0379,0.9637,0.0106,0.0005</t>
+  </si>
+  <si>
+    <t>0.0060,0.9936,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.2770,0.0121,0.8433,0.0023</t>
+  </si>
+  <si>
+    <t>0.8286,0.0631,0.1113,0.0067</t>
+  </si>
+  <si>
+    <t>0.0073,0.0038,0.9891,0.0037</t>
+  </si>
+  <si>
+    <t>0.0009,0.8665,0.9844,0.0004</t>
+  </si>
+  <si>
+    <t>0.0090,0.9318,0.3595,0.0054</t>
+  </si>
+  <si>
+    <t>0.0010,0.9938,0.2342,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9881,0.5628,0.0008</t>
+  </si>
+  <si>
+    <t>0.0366,0.0007,0.0031,0.9816</t>
+  </si>
+  <si>
+    <t>0.0009,0.0015,0.0006,0.9990</t>
+  </si>
+  <si>
+    <t>0.0033,0.0002,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.0106,0.0156,0.0042,0.9910</t>
+  </si>
+  <si>
+    <t>0.0060,0.0009,0.0020,0.9960</t>
+  </si>
+  <si>
+    <t>0.0046,0.0136,0.0008,0.9960</t>
+  </si>
+  <si>
+    <t>0.0024,0.9517,0.8707,0.0019</t>
+  </si>
+  <si>
+    <t>0.0069,0.1559,0.9886,0.0006</t>
+  </si>
+  <si>
+    <t>0.0164,0.1489,0.8962,0.0036</t>
+  </si>
+  <si>
+    <t>0.0054,0.7825,0.9816,0.0030</t>
+  </si>
+  <si>
+    <t>0.0003,0.9940,0.4877,0.0001</t>
+  </si>
+  <si>
+    <t>0.0121,0.8464,0.6233,0.0044</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9823,0.0137,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.9668,0.0442,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9907,0.0018,0.0002,0.0034</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9863,0.0058,0.0030,0.0021</t>
+  </si>
+  <si>
+    <t>0.9916,0.0093,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9952,0.0011,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0008,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0103,0.0037,0.9889,0.0011</t>
+  </si>
+  <si>
+    <t>0.0080,0.0027,0.9846,0.0043</t>
+  </si>
+  <si>
+    <t>0.8969,0.0033,0.1504,0.0044</t>
+  </si>
+  <si>
+    <t>0.0022,0.0012,0.9954,0.0019</t>
+  </si>
+  <si>
+    <t>0.0019,0.9956,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.0012,0.9973,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.1079,0.9087,0.0065,0.0043</t>
+  </si>
+  <si>
+    <t>0.0944,0.9367,0.0062,0.0020</t>
+  </si>
+  <si>
+    <t>0.0077,0.9891,0.0025,0.0012</t>
+  </si>
+  <si>
+    <t>0.0020,0.9962,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.6047,0.6298,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.6658,0.0385,0.2923,0.0425</t>
+  </si>
+  <si>
+    <t>0.1052,0.0011,0.9063,0.0053</t>
+  </si>
+  <si>
+    <t>0.7207,0.0091,0.3166,0.0156</t>
+  </si>
+  <si>
+    <t>0.1936,0.0054,0.8748,0.0044</t>
+  </si>
+  <si>
+    <t>0.1108,0.4498,0.2235,0.4434</t>
+  </si>
+  <si>
+    <t>0.0019,0.9956,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.9972,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.0043,0.9848,0.0088,0.0057</t>
+  </si>
+  <si>
+    <t>0.0011,0.5082,0.9273,0.0031</t>
+  </si>
+  <si>
+    <t>0.0069,0.9909,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.8539,0.1633,0.0130,0.0024</t>
+  </si>
+  <si>
+    <t>0.8177,0.2485,0.0060,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0022,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9705,0.0052,0.0256,0.0023</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9912,0.0008,0.0080,0.0006</t>
+  </si>
+  <si>
+    <t>0.9965,0.0003,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0008,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.0055,0.1384,0.9787,0.0046</t>
+  </si>
+  <si>
+    <t>0.0014,0.3124,0.9938,0.0005</t>
+  </si>
+  <si>
+    <t>0.0253,0.0127,0.9647,0.0029</t>
+  </si>
+  <si>
+    <t>0.0412,0.0978,0.9293,0.0106</t>
+  </si>
+  <si>
+    <t>0.9929,0.0004,0.0073,0.0002</t>
+  </si>
+  <si>
+    <t>0.9737,0.0047,0.0079,0.0031</t>
+  </si>
+  <si>
+    <t>0.5455,0.0011,0.6655,0.0003</t>
+  </si>
+  <si>
+    <t>0.9395,0.0047,0.1024,0.0011</t>
+  </si>
+  <si>
+    <t>0.2368,0.0003,0.0012,0.9340</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0025,0.9989</t>
+  </si>
+  <si>
+    <t>0.0006,0.0116,0.0012,0.9985</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.0002,0.9992</t>
+  </si>
+  <si>
+    <t>0.0006,0.9920,0.3285,0.0009</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.4105,0.6766,0.0066,0.0086</t>
+  </si>
+  <si>
+    <t>0.9959,0.0005,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.4592,0.6477,0.0053,0.0026</t>
+  </si>
+  <si>
+    <t>0.9722,0.0023,0.0038,0.0141</t>
+  </si>
+  <si>
+    <t>0.7838,0.0156,0.0355,0.1886</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.0161,0.9589,0.1947</t>
+  </si>
+  <si>
+    <t>0.7811,0.0003,0.0019,0.3646</t>
+  </si>
+  <si>
+    <t>0.9690,0.0012,0.0007,0.0254</t>
+  </si>
+  <si>
+    <t>0.1093,0.8926,0.0232,0.0023</t>
+  </si>
+  <si>
+    <t>0.9648,0.0126,0.0085,0.0023</t>
+  </si>
+  <si>
+    <t>0.9803,0.0124,0.0048,0.0008</t>
+  </si>
+  <si>
+    <t>0.4606,0.4934,0.0126,0.0222</t>
+  </si>
+  <si>
+    <t>0.9703,0.0251,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.9903,0.0061,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9962,0.0012,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0015,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0009,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9925,0.0007,0.0003,0.0036</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9957,0.0003,0.0001,0.0028</t>
+  </si>
+  <si>
+    <t>0.8791,0.1938,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.8884,0.1217,0.0039,0.0027</t>
+  </si>
+  <si>
+    <t>0.8926,0.1714,0.0020,0.0013</t>
+  </si>
+  <si>
+    <t>0.0151,0.5654,0.9689,0.0043</t>
+  </si>
+  <si>
+    <t>0.9787,0.0287,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9671,0.0090,0.0076,0.0055</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.6883,0.3705,0.0027,0.0076</t>
+  </si>
+  <si>
+    <t>0.0010,0.0094,0.9976,0.0013</t>
+  </si>
+  <si>
+    <t>0.9109,0.0353,0.0424,0.0025</t>
+  </si>
+  <si>
+    <t>0.0107,0.0031,0.9876,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.2651,0.9910,0.0030</t>
+  </si>
+  <si>
+    <t>0.0111,0.0025,0.9873,0.0012</t>
+  </si>
+  <si>
+    <t>0.0035,0.0107,0.9950,0.0012</t>
+  </si>
+  <si>
+    <t>0.0017,0.0010,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.0050,0.0009,0.9936,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.0066,0.9940,0.0036</t>
+  </si>
+  <si>
+    <t>0.0687,0.0114,0.8883,0.0212</t>
+  </si>
+  <si>
+    <t>0.7686,0.0279,0.2499,0.0044</t>
+  </si>
+  <si>
+    <t>0.7012,0.0187,0.4212,0.0043</t>
+  </si>
+  <si>
+    <t>0.0239,0.6424,0.2345,0.0005</t>
+  </si>
+  <si>
+    <t>0.2153,0.3341,0.2718,0.0105</t>
+  </si>
+  <si>
+    <t>0.7797,0.0436,0.1760,0.0033</t>
+  </si>
+  <si>
+    <t>0.4754,0.0750,0.4483,0.0212</t>
+  </si>
+  <si>
+    <t>0.0897,0.0084,0.9267,0.0021</t>
+  </si>
+  <si>
+    <t>0.1714,0.8880,0.0057,0.0016</t>
+  </si>
+  <si>
+    <t>0.0543,0.9638,0.0008,0.0027</t>
+  </si>
+  <si>
+    <t>0.1119,0.9296,0.0005,0.0037</t>
+  </si>
+  <si>
+    <t>0.9786,0.0223,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9731,0.0209,0.0011,0.0029</t>
+  </si>
+  <si>
+    <t>0.9245,0.0217,0.0516,0.0024</t>
+  </si>
+  <si>
+    <t>0.9877,0.0011,0.0110,0.0004</t>
+  </si>
+  <si>
+    <t>0.8929,0.0103,0.0238,0.0428</t>
+  </si>
+  <si>
+    <t>0.7603,0.0245,0.2401,0.0196</t>
+  </si>
+  <si>
+    <t>0.5379,0.0037,0.3791,0.0370</t>
+  </si>
+  <si>
+    <t>0.0164,0.0100,0.9754,0.0084</t>
+  </si>
+  <si>
+    <t>0.0128,0.0223,0.9398,0.0357</t>
+  </si>
+  <si>
+    <t>0.2031,0.1343,0.7662,0.0234</t>
+  </si>
+  <si>
+    <t>0.0211,0.0177,0.9670,0.0050</t>
+  </si>
+  <si>
+    <t>0.0050,0.0387,0.9680,0.0064</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9933,0.0026,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9871,0.0085,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9913,0.0050,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0034,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.0722,0.9954,0.0007</t>
+  </si>
+  <si>
+    <t>0.1892,0.0838,0.7554,0.0036</t>
+  </si>
+  <si>
+    <t>0.9798,0.0017,0.0140,0.0018</t>
+  </si>
+  <si>
+    <t>0.0015,0.0016,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0013,0.9939,0.0179</t>
+  </si>
+  <si>
+    <t>0.0010,0.0465,0.9946,0.0030</t>
+  </si>
+  <si>
+    <t>0.0010,0.0018,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.0077,0.0009,0.9854,0.0035</t>
+  </si>
+  <si>
+    <t>0.0030,0.0035,0.9907,0.0037</t>
+  </si>
+  <si>
+    <t>0.0056,0.0027,0.9951,0.0002</t>
+  </si>
+  <si>
+    <t>0.1530,0.0026,0.9030,0.0017</t>
+  </si>
+  <si>
+    <t>0.8317,0.0073,0.1732,0.0139</t>
+  </si>
+  <si>
+    <t>0.7826,0.0080,0.1949,0.0304</t>
+  </si>
+  <si>
+    <t>0.9874,0.0008,0.0144,0.0003</t>
+  </si>
+  <si>
+    <t>0.9915,0.0058,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9888,0.0078,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9966,0.0002,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9916,0.0068,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.0287,0.2690,0.9177,0.0023</t>
+  </si>
+  <si>
+    <t>0.0022,0.0179,0.9948,0.0006</t>
+  </si>
+  <si>
+    <t>0.0076,0.0032,0.9869,0.0015</t>
+  </si>
+  <si>
+    <t>0.0767,0.0101,0.9410,0.0012</t>
+  </si>
+  <si>
+    <t>0.0014,0.0015,0.9975,0.0005</t>
+  </si>
+  <si>
+    <t>0.0105,0.0456,0.9520,0.0623</t>
+  </si>
+  <si>
+    <t>0.1170,0.0041,0.8936,0.0072</t>
+  </si>
+  <si>
+    <t>0.5340,0.0247,0.4160,0.0440</t>
+  </si>
+  <si>
+    <t>0.8684,0.0010,0.0087,0.0933</t>
+  </si>
+  <si>
+    <t>0.0491,0.0016,0.0051,0.9750</t>
+  </si>
+  <si>
+    <t>0.4313,0.0066,0.0023,0.7223</t>
+  </si>
+  <si>
+    <t>0.0062,0.0001,0.0004,0.9976</t>
+  </si>
+  <si>
+    <t>0.0034,0.0002,0.0011,0.9976</t>
+  </si>
+  <si>
+    <t>0.9915,0.0005,0.0018,0.0024</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
